--- a/WHR_Comparison_2024_vs_2025.xlsx
+++ b/WHR_Comparison_2024_vs_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Excel and PowerBi pract\DA Final CP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99071B77-AEAC-4E62-9404-9F9469911A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA025E7C-AC34-4949-8215-B35FD8CBE283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{33B90399-4645-4CE8-AC53-6ADF6E05C218}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{33B90399-4645-4CE8-AC53-6ADF6E05C218}"/>
   </bookViews>
   <sheets>
     <sheet name="WHR_Comparison_2024_vs_2025" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="185">
   <si>
     <t>Country</t>
   </si>
@@ -573,6 +573,9 @@
   </si>
   <si>
     <t>WHR_Comparison_2024 vs 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -8104,7 +8107,7 @@
   <wetp:taskpane dockstate="right" visibility="0" width="438" row="5">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="8">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="5">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -15327,82 +15330,85 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN33" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:40" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>184</v>
+      </c>
       <c r="AN34" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN36" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN38" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN39" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN40" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN41" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN42" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN44" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN45" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN46" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN47" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="40:40" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:40" x14ac:dyDescent="0.3">
       <c r="AN48" t="s">
         <v>63</v>
       </c>
